--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="Q2" t="n">
-        <v>227</v>
+        <v>586</v>
       </c>
       <c r="R2" t="n">
-        <v>510</v>
+        <v>835</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -718,10 +722,10 @@
         <v>278</v>
       </c>
       <c r="Q3" t="n">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="R3" t="n">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q4" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="R4" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
         <v>398</v>
       </c>
       <c r="R5" t="n">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q6" t="n">
         <v>62</v>
       </c>
       <c r="R6" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1217,34 +1221,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>249</v>
+        <v>75</v>
       </c>
       <c r="Q9" t="n">
-        <v>586</v>
+        <v>1035</v>
       </c>
       <c r="R9" t="n">
-        <v>835</v>
+        <v>1110</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1315,44 +1315,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H 퍼스널트레이닝 한남</t>
+          <t>에이블짐 이태원점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hp4566@naver.com</t>
+          <t>ablegym11@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-4566</t>
+          <t>0507-1469-8181</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 76 403호</t>
+          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hp4566</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>757</v>
       </c>
       <c r="Q10" t="n">
-        <v>162</v>
+        <v>658</v>
       </c>
       <c r="R10" t="n">
-        <v>175</v>
+        <v>1415</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35058160</t>
+          <t>1674730307</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35058160</t>
+          <t>https://m.place.naver.com/place/1674730307</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="Q11" t="n">
         <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q2" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="R2" t="n">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>278</v>
+        <v>718</v>
       </c>
       <c r="Q3" t="n">
-        <v>1040</v>
+        <v>327</v>
       </c>
       <c r="R3" t="n">
-        <v>1318</v>
+        <v>1045</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>706</v>
+        <v>273</v>
       </c>
       <c r="Q4" t="n">
-        <v>324</v>
+        <v>967</v>
       </c>
       <c r="R4" t="n">
-        <v>1030</v>
+        <v>1240</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="Q6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="R6" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1038,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에스웨이 피트니스 한남점</t>
+          <t>팀하드피트니스 한남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>s_wayhn@naver.com</t>
+          <t>teamhardfitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02-795-0117</t>
+          <t>0507-1310-4252</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 70 지하 1층</t>
+          <t>서울특별시 용산구 독서당로 67 402호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s_wayhn</t>
+          <t>https://blog.naver.com/teamhardfitness</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>170</v>
+        <v>89</v>
       </c>
       <c r="Q7" t="n">
-        <v>223</v>
+        <v>107</v>
       </c>
       <c r="R7" t="n">
-        <v>393</v>
+        <v>196</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,51 +1110,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1787209299</t>
+          <t>1132822818</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1787209299</t>
+          <t>https://m.place.naver.com/place/1132822818</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘피PT&amp;필라테스</t>
+          <t>마이트레이너짐 PT 한남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>leo920617@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1318-8437</t>
+          <t>0507-1477-2603</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
+          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lp.pt_pilates</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>135</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>331</v>
+        <v>6</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1420244365</t>
+          <t>2084933660</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420244365</t>
+          <t>https://m.place.naver.com/place/2084933660</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1226,34 +1226,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>마이트레이너짐 PT 이태원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1347-2166</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="n">
-        <v>1035</v>
+        <v>185</v>
       </c>
       <c r="R9" t="n">
-        <v>1110</v>
+        <v>273</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>1307063449</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/1307063449</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이블짐 이태원점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ablegym11@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1469-8181</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>757</v>
+        <v>76</v>
       </c>
       <c r="Q10" t="n">
-        <v>658</v>
+        <v>1044</v>
       </c>
       <c r="R10" t="n">
-        <v>1415</v>
+        <v>1120</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,56 +1392,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1674730307</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674730307</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스카이짐 GDR 골프아카데미 &amp; 헬스</t>
+          <t>에이블짐 이태원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bestfitnessno1@naver.com</t>
+          <t>ablegym11@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-7457</t>
+          <t>0507-1469-8181</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 273 B1 스카이짐</t>
+          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bestfitnessno1</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>984</v>
+        <v>756</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>656</v>
       </c>
       <c r="R11" t="n">
-        <v>1151</v>
+        <v>1412</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1317998488</t>
+          <t>1674730307</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1317998488</t>
+          <t>https://m.place.naver.com/place/1674730307</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="Q2" t="n">
-        <v>587</v>
+        <v>227</v>
       </c>
       <c r="R2" t="n">
-        <v>838</v>
+        <v>514</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q3" t="n">
         <v>327</v>
       </c>
       <c r="R3" t="n">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Q4" t="n">
-        <v>967</v>
+        <v>998</v>
       </c>
       <c r="R4" t="n">
-        <v>1240</v>
+        <v>1269</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -838,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -932,7 +928,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="R6" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1022,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1094,10 @@
         <v>89</v>
       </c>
       <c r="Q7" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R7" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1120,7 +1116,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1210,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1226,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 이태원점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-2166</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q9" t="n">
-        <v>185</v>
+        <v>1045</v>
       </c>
       <c r="R9" t="n">
-        <v>273</v>
+        <v>1122</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,56 +1294,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1307063449</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1307063449</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>엘피PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>leo920617@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1318-8437</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>https://www.instagram.com/lp.pt_pilates</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="Q10" t="n">
-        <v>1044</v>
+        <v>136</v>
       </c>
       <c r="R10" t="n">
-        <v>1120</v>
+        <v>333</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>1420244365</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/1420244365</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이블짐 이태원점</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ablegym11@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1469-8181</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,15 +1447,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>756</v>
+        <v>252</v>
       </c>
       <c r="Q11" t="n">
-        <v>656</v>
+        <v>587</v>
       </c>
       <c r="R11" t="n">
-        <v>1412</v>
+        <v>839</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,17 +1486,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1674730307</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674730307</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -427,12 +427,12 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="Q2" t="n">
-        <v>227</v>
+        <v>587</v>
       </c>
       <c r="R2" t="n">
-        <v>514</v>
+        <v>839</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +710,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>719</v>
+        <v>287</v>
       </c>
       <c r="Q3" t="n">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="R3" t="n">
-        <v>1046</v>
+        <v>514</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +793,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4774o</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>271</v>
+        <v>719</v>
       </c>
       <c r="Q4" t="n">
-        <v>998</v>
+        <v>327</v>
       </c>
       <c r="R4" t="n">
-        <v>1269</v>
+        <v>1046</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +832,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +854,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46xvw</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="n">
-        <v>398</v>
+        <v>1018</v>
       </c>
       <c r="R5" t="n">
-        <v>504</v>
+        <v>1289</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>웰페리온 SPA &amp; FITNESS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>wellperion@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1467-1339</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울 용산구 서빙고로 413</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://litt.ly/wellperion</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41ise</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>398</v>
       </c>
       <c r="R6" t="n">
-        <v>153</v>
+        <v>504</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>1048457693</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/1048457693</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀하드피트니스 한남점</t>
+          <t>MCTGYM용문</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teamhardfitness@naver.com</t>
+          <t>mctfitness7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1310-4252</t>
+          <t>0507-1423-7537</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 402호</t>
+          <t>서울 용산구 원효로41길 69 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamhardfitness</t>
+          <t>https://mctgym.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wn6s8fj</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q7" t="n">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="R7" t="n">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1132822818</t>
+          <t>2031556968</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132822818</t>
+          <t>https://m.place.naver.com/place/2031556968</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 한남점</t>
+          <t>팀하드피트니스 한남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>teamhardfitness@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1477-2603</t>
+          <t>0507-1310-4252</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
+          <t>서울 용산구 독서당로 67 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://blog.naver.com/teamhardfitness</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3is9fs</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>197</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2084933660</t>
+          <t>1132822818</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084933660</t>
+          <t>https://m.place.naver.com/place/1132822818</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,34 +1246,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>마이트레이너짐 PT 한남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1477-2603</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울 용산구 독서당로 71 지1층 2호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1264,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w8u9zz6</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>1045</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1122</v>
+        <v>6</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>2084933660</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/2084933660</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘피PT&amp;필라테스</t>
+          <t>마이트레이너짐 PT 이태원점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>leo920617@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1318-8437</t>
+          <t>0507-1347-2166</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
+          <t>서울 용산구 보광로59길 40 202호 마이트레이너짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lp.pt_pilates</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wp3uisj</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>197</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="n">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="R10" t="n">
-        <v>333</v>
+        <v>273</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1420244365</t>
+          <t>1307063449</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420244365</t>
+          <t>https://m.place.naver.com/place/1307063449</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1457,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
+          <t>https://talk.naver.com/ct/w40j6t</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1471,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>587</v>
+        <v>1045</v>
       </c>
       <c r="R11" t="n">
-        <v>839</v>
+        <v>1122</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -657,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -710,7 +710,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>719</v>
+        <v>287</v>
       </c>
       <c r="Q3" t="n">
-        <v>328</v>
+        <v>227</v>
       </c>
       <c r="R3" t="n">
-        <v>1047</v>
+        <v>514</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -756,34 +756,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>106</v>
+        <v>719</v>
       </c>
       <c r="Q4" t="n">
-        <v>398</v>
+        <v>329</v>
       </c>
       <c r="R4" t="n">
-        <v>504</v>
+        <v>1048</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>웰페리온 SPA &amp; FITNESS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>wellperion@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1467-1339</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 서빙고로 413</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://litt.ly/wellperion</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>1028</v>
+        <v>398</v>
       </c>
       <c r="R5" t="n">
-        <v>1299</v>
+        <v>504</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1048457693</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1048457693</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>271</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>1038</v>
       </c>
       <c r="R6" t="n">
-        <v>156</v>
+        <v>1309</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>크로스핏 알앤엘 용산</t>
+          <t>MCTGYM용문</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>crossfitrnl_su@naver.com</t>
+          <t>mctfitness7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-8898</t>
+          <t>0507-1423-7537</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 295 B1층</t>
+          <t>서울특별시 용산구 원효로41길 69 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/crossfit_rnl_yongsan</t>
+          <t>https://mctgym.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>127</v>
+        <v>86</v>
       </c>
       <c r="Q7" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="R7" t="n">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1771175314</t>
+          <t>2031556968</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1771175314</t>
+          <t>https://m.place.naver.com/place/2031556968</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 한남점</t>
+          <t>마이 페이보릿 리커버리</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>athletetraininglab@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1477-2603</t>
+          <t>0507-1356-4024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
+          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://blog.naver.com/athletetraininglab</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,297 +1204,15 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2084933660</t>
+          <t>1046370565</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084933660</t>
+          <t>https://m.place.naver.com/place/1046370565</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>민트니스</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>mintness0218@naver.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1367-5479</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://naver.me/xExbOq0i</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1046</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1123</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>1620428153</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>H 퍼스널트레이닝 한남</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>hp4566@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1419-4566</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 대사관로 76 403호</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/hp4566</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>162</v>
-      </c>
-      <c r="R10" t="n">
-        <v>175</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>35058160</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/35058160</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>실내골프연습장</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>스카이짐 GDR 골프아카데미 &amp; 헬스</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>bestfitnessno1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1313-7457</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 한강대로 273 B1 스카이짐</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bestfitnessno1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>997</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>167</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1164</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1317998488</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1317998488</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>apexjon519@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -684,17 +684,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4774o</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -850,39 +854,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -892,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46xvw</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -907,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="n">
-        <v>398</v>
+        <v>1038</v>
       </c>
       <c r="R5" t="n">
-        <v>504</v>
+        <v>1309</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +930,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -944,34 +952,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>웰페리온 SPA &amp; FITNESS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>wellperion@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1467-1339</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 서빙고로 413</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://litt.ly/wellperion</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -986,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w41ise</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1001,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="Q6" t="n">
-        <v>1038</v>
+        <v>398</v>
       </c>
       <c r="R6" t="n">
-        <v>1309</v>
+        <v>504</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1028,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1048457693</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1048457693</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1080,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wn6s8fj</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1132,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이 페이보릿 리커버리</t>
+          <t>팀하드피트니스 한남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>athletetraininglab@naver.com</t>
+          <t>banana_hannam@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1356-4024</t>
+          <t>0507-1310-4252</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
+          <t>서울특별시 용산구 독서당로 67 402호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athletetraininglab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,20 +1180,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3is9fs</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="R8" t="n">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,15 +1224,305 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1046370565</t>
+          <t>1132822818</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046370565</t>
+          <t>https://m.place.naver.com/place/1132822818</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>민트니스</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mintness0218@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1367-5479</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40j6t</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1047</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1124</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1620428153</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1620428153</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>에이블짐 이태원점</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ablegym11@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1469-8181</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>656</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1413</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1674730307</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674730307</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H 퍼스널트레이닝 한남</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hp4566@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1419-4566</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로 76 403호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4tn2d</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>162</v>
+      </c>
+      <c r="R11" t="n">
+        <v>175</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>35058160</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35058160</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="49" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apexjon519@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="Q2" t="n">
-        <v>587</v>
+        <v>227</v>
       </c>
       <c r="R2" t="n">
-        <v>839</v>
+        <v>514</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -710,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>287</v>
+        <v>719</v>
       </c>
       <c r="Q3" t="n">
-        <v>227</v>
+        <v>329</v>
       </c>
       <c r="R3" t="n">
-        <v>514</v>
+        <v>1048</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +784,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4774o</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -817,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>719</v>
+        <v>271</v>
       </c>
       <c r="Q4" t="n">
-        <v>329</v>
+        <v>1038</v>
       </c>
       <c r="R4" t="n">
-        <v>1048</v>
+        <v>1309</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -854,39 +846,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>웰페리온 SPA &amp; FITNESS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>wellperion@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1467-1339</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 서빙고로 413</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://litt.ly/wellperion</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -896,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w46xvw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -915,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>271</v>
+        <v>106</v>
       </c>
       <c r="Q5" t="n">
-        <v>1038</v>
+        <v>398</v>
       </c>
       <c r="R5" t="n">
-        <v>1309</v>
+        <v>504</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1048457693</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1048457693</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -952,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>MCTGYM용문</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>mctfitness7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1423-7537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울특별시 용산구 원효로41길 69 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>https://mctgym.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -994,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41ise</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1013,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
-        <v>504</v>
+        <v>157</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>2031556968</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/2031556968</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1050,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>팀하드피트니스 한남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>teamhardfitness@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1310-4252</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울특별시 용산구 독서당로 67 402호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://blog.naver.com/teamhardfitness</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1092,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wn6s8fj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="R7" t="n">
-        <v>156</v>
+        <v>198</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>1132822818</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/1132822818</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1148,39 +1128,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>팀하드피트니스 한남점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>banana_hannam@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1310-4252</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 402호</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1190,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w3is9fs</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="Q8" t="n">
-        <v>108</v>
+        <v>1047</v>
       </c>
       <c r="R8" t="n">
-        <v>197</v>
+        <v>1124</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,61 +1200,61 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1132822818</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132822818</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1293,7 +1269,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40j6t</t>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="Q9" t="n">
-        <v>1047</v>
+        <v>586</v>
       </c>
       <c r="R9" t="n">
-        <v>1124</v>
+        <v>838</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,61 +1298,61 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이블짐 이태원점</t>
+          <t>H 퍼스널트레이닝 한남</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ablegym11@naver.com</t>
+          <t>hp4566@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1469-8181</t>
+          <t>0507-1419-4566</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+          <t>서울특별시 용산구 대사관로 76 403호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+          <t>https://blog.naver.com/hp4566</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1401,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>757</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>656</v>
+        <v>162</v>
       </c>
       <c r="R10" t="n">
-        <v>1413</v>
+        <v>175</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,51 +1392,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1674730307</t>
+          <t>35058160</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1674730307</t>
+          <t>https://m.place.naver.com/place/35058160</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H 퍼스널트레이닝 한남</t>
+          <t>스카이짐 GDR 골프아카데미 &amp; 헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hp4566@naver.com</t>
+          <t>bestfitnessno1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1419-4566</t>
+          <t>0507-1313-7457</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 76 403호</t>
+          <t>서울특별시 용산구 한강대로 273 B1 스카이짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bestfitnessno1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1470,24 +1446,20 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4tn2d</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1499,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Q11" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="R11" t="n">
-        <v>175</v>
+        <v>1167</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,17 +1486,115 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>35058160</t>
+          <t>1317998488</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35058160</t>
+          <t>https://m.place.naver.com/place/1317998488</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>인터내셔널 필라테스</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>internationalpilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1339-2733</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>서울 용산구 독서당로 78 고은빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/international.pilates</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w28iu2f</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>117</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1650827956</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650827956</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,13 +606,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>287</v>
+        <v>252</v>
       </c>
       <c r="Q2" t="n">
-        <v>227</v>
+        <v>586</v>
       </c>
       <c r="R2" t="n">
-        <v>514</v>
+        <v>838</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,39 +657,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -706,7 +710,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>719</v>
+        <v>287</v>
       </c>
       <c r="Q3" t="n">
-        <v>329</v>
+        <v>227</v>
       </c>
       <c r="R3" t="n">
-        <v>1048</v>
+        <v>514</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +734,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +793,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>271</v>
+        <v>719</v>
       </c>
       <c r="Q4" t="n">
-        <v>1038</v>
+        <v>329</v>
       </c>
       <c r="R4" t="n">
-        <v>1309</v>
+        <v>1048</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -940,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>271</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>1056</v>
       </c>
       <c r="R6" t="n">
-        <v>157</v>
+        <v>1327</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,34 +1038,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>팀하드피트니스 한남점</t>
+          <t>MCTGYM용문</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>teamhardfitness@naver.com</t>
+          <t>mctfitness7@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1310-4252</t>
+          <t>0507-1423-7537</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 67 402호</t>
+          <t>서울특별시 용산구 원효로41길 69 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamhardfitness</t>
+          <t>https://mctgym.com</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="Q7" t="n">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1110,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1132822818</t>
+          <t>2031556968</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132822818</t>
+          <t>https://m.place.naver.com/place/2031556968</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>마이 페이보릿 리커버리</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>athletetraininglab@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1356-4024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>https://blog.naver.com/athletetraininglab</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,7 +1169,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1181,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>1047</v>
+        <v>34</v>
       </c>
       <c r="R8" t="n">
-        <v>1124</v>
+        <v>75</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1204,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>1046370565</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/1046370565</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,39 +1221,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>마이트레이너짐 PT 한남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1477-2603</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1264,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>252</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>586</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>838</v>
+        <v>6</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>2084933660</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/2084933660</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1320,29 +1320,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H 퍼스널트레이닝 한남</t>
+          <t>마이트레이너짐 PT 이태원점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hp4566@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-4566</t>
+          <t>0507-1347-2166</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 대사관로 76 403호</t>
+          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hp4566</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="Q10" t="n">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="R10" t="n">
-        <v>175</v>
+        <v>273</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35058160</t>
+          <t>1307063449</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35058160</t>
+          <t>https://m.place.naver.com/place/1307063449</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,39 +1409,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스카이짐 GDR 골프아카데미 &amp; 헬스</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bestfitnessno1@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1313-7457</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 한강대로 273 B1 스카이짐</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bestfitnessno1</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1000</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>1048</v>
       </c>
       <c r="R11" t="n">
-        <v>1167</v>
+        <v>1125</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1317998488</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1317998488</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1503,34 +1503,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>인터내셔널 필라테스</t>
+          <t>엘피PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>internationalpilates@naver.com</t>
+          <t>leo920617@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1339-2733</t>
+          <t>0507-1318-8437</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 용산구 독서당로 78 고은빌딩 5층</t>
+          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/international.pilates</t>
+          <t>https://www.instagram.com/lp.pt_pilates</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1550,14 +1550,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w28iu2f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1569,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="Q12" t="n">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="R12" t="n">
-        <v>117</v>
+        <v>334</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1584,15 +1580,109 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1650827956</t>
+          <t>1420244365</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650827956</t>
+          <t>https://m.place.naver.com/place/1420244365</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>에이블짐 이태원점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ablegym11@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1469-8181</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>656</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1413</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1674730307</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674730307</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>원짐</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>1_gym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>0507-1350-0173</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>https://pf.kakao.com/_HXJLxj</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,17 +606,13 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="Q2" t="n">
-        <v>586</v>
+        <v>227</v>
       </c>
       <c r="R2" t="n">
-        <v>838</v>
+        <v>514</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,56 +636,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>1463535348</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/1463535348</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>이태원짐</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>itaewon_gym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1375-3752</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>https://blog.naver.com/itaewon_gym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -710,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>287</v>
+        <v>720</v>
       </c>
       <c r="Q3" t="n">
-        <v>227</v>
+        <v>329</v>
       </c>
       <c r="R3" t="n">
-        <v>514</v>
+        <v>1049</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1379530021</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1379530021</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -756,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>웰페리온 SPA &amp; FITNESS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>wellperion@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1467-1339</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 서빙고로 413</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>https://litt.ly/wellperion</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -793,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>719</v>
+        <v>106</v>
       </c>
       <c r="Q4" t="n">
-        <v>329</v>
+        <v>398</v>
       </c>
       <c r="R4" t="n">
-        <v>1048</v>
+        <v>504</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1048457693</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1048457693</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -850,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>MCTGYM 용산</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>mctfitness3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1375-7537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>https://youtube.com/@mct12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -907,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>106</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="n">
-        <v>398</v>
+        <v>1056</v>
       </c>
       <c r="R5" t="n">
-        <v>504</v>
+        <v>1327</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>1407110482</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/1407110482</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>MCTGYM용문</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>mctfitness7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1423-7537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 원효로41길 69 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://mctgym.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1001,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>271</v>
+        <v>86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1056</v>
+        <v>71</v>
       </c>
       <c r="R6" t="n">
-        <v>1327</v>
+        <v>157</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>2031556968</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/2031556968</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1038,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>마이 페이보릿 리커버리</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>athletetraininglab@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1356-4024</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://blog.naver.com/athletetraininglab</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>1046370565</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/1046370565</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이 페이보릿 리커버리</t>
+          <t>마이트레이너짐 PT 한남점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>athletetraininglab@naver.com</t>
+          <t>mytrainergym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1356-4024</t>
+          <t>0507-1477-2603</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
+          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athletetraininglab</t>
+          <t>https://linktr.ee/mytrainergym105</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1169,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,17 +1181,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1046370565</t>
+          <t>2084933660</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046370565</t>
+          <t>https://m.place.naver.com/place/2084933660</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1222,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 한남점</t>
+          <t>마이트레이너짐 PT 이태원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1237,13 +1233,13 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1477-2603</t>
+          <t>0507-1347-2166</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
+          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1283,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>273</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2084933660</t>
+          <t>1307063449</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084933660</t>
+          <t>https://m.place.naver.com/place/1307063449</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1320,34 +1316,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 이태원점</t>
+          <t>민트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>mintness0218@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1347-2166</t>
+          <t>0507-1367-5479</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://naver.me/xExbOq0i</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1377,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="Q10" t="n">
-        <v>185</v>
+        <v>1048</v>
       </c>
       <c r="R10" t="n">
-        <v>273</v>
+        <v>1125</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,56 +1388,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1307063449</t>
+          <t>1620428153</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1307063449</t>
+          <t>https://m.place.naver.com/place/1620428153</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>엘피PT&amp;필라테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>leo920617@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>0507-1318-8437</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>https://www.instagram.com/lp.pt_pilates</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1471,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="Q11" t="n">
-        <v>1048</v>
+        <v>137</v>
       </c>
       <c r="R11" t="n">
-        <v>1125</v>
+        <v>334</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,56 +1482,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>1420244365</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/1420244365</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘피PT&amp;필라테스</t>
+          <t>에이펙스 이엠에스 스튜디오 용산점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>leo920617@naver.com</t>
+          <t>apexems1@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1318-8437</t>
+          <t>0507-1489-0892</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
+          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lp.pt_pilates</t>
+          <t>http://apexems.creatorlink.net/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1550,10 +1546,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w3t5</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="Q12" t="n">
-        <v>137</v>
+        <v>586</v>
       </c>
       <c r="R12" t="n">
-        <v>334</v>
+        <v>838</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,111 +1580,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1420244365</t>
+          <t>1672804681</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420244365</t>
+          <t>https://m.place.naver.com/place/1672804681</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>에이블짐 이태원점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ablegym11@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1469-8181</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>757</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>656</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1413</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1674730307</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1674730307</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/용산_PT.xlsx
+++ b/naver-place-crawler/results_health/용산_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>원짐</t>
+          <t>리암스짐 한남</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1_gym@naver.com</t>
+          <t>liamsgym@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-0173</t>
+          <t>0507-1443-8487</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이촌로 1 1층 104호, 지하 1층 전체</t>
+          <t>서울특별시 용산구 한남대로42길 33 1층 리암스짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_HXJLxj</t>
+          <t>https://www.instagram.com/liams__gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,7 +612,7 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
-        <v>514</v>
+        <v>42</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1463535348</t>
+          <t>1959666773</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1463535348</t>
+          <t>https://m.place.naver.com/place/1959666773</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>이태원짐</t>
+          <t>피티플렉스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>itaewon_gym@naver.com</t>
+          <t>fitflex@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1375-3752</t>
+          <t>0507-1357-0881</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+          <t>서울특별시 용산구 효창원로69길 25 1층 피티플렉스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/itaewon_gym</t>
+          <t>http://www.instagram.com/pt_flex</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>720</v>
+        <v>16</v>
       </c>
       <c r="Q3" t="n">
-        <v>329</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1049</v>
+        <v>21</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1379530021</t>
+          <t>1267127462</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379530021</t>
+          <t>https://m.place.naver.com/place/1267127462</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,39 +752,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>웰페리온 SPA &amp; FITNESS</t>
+          <t>자스민스튜디오 체형교정+운동센터</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wellperion@naver.com</t>
+          <t>shopin_korea@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1467-1339</t>
+          <t>0507-1429-5994</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 서빙고로 413</t>
+          <t>서울특별시 용산구 한강대로 69 업무동</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/wellperion</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>398</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>504</v>
+        <v>26</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1048457693</t>
+          <t>1191178692</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048457693</t>
+          <t>https://m.place.naver.com/place/1191178692</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCTGYM 용산</t>
+          <t>Kraft PT Studio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mctfitness3@naver.com</t>
+          <t>shopin_korea@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1375-7537</t>
+          <t>0507-1315-1983</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+          <t>서울특별시 용산구 신흥로20길 17 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com/@mct12</t>
+          <t>https://www.instagram.com/kraftptstudio</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>271</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1056</v>
+        <v>13</v>
       </c>
       <c r="R5" t="n">
-        <v>1327</v>
+        <v>14</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1407110482</t>
+          <t>1298962921</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1407110482</t>
+          <t>https://m.place.naver.com/place/1298962921</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCTGYM용문</t>
+          <t>좋은습관 PT STUDIO 용산</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mctfitness7@naver.com</t>
+          <t>goodhabitone@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1423-7537</t>
+          <t>0507-1417-1531</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 원효로41길 69 3층</t>
+          <t>서울특별시 용산구 원효로 214 한보빌딩 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://mctgym.com</t>
+          <t>https://zrr.kr/h1b6Hw</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>86</v>
+        <v>452</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="R6" t="n">
-        <v>157</v>
+        <v>546</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2031556968</t>
+          <t>658580010</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2031556968</t>
+          <t>https://m.place.naver.com/place/658580010</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이 페이보릿 리커버리</t>
+          <t>비고핏</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>athletetraininglab@naver.com</t>
+          <t>tkfkd1219-@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1356-4024</t>
+          <t>0507-1304-8033</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
+          <t>서울특별시 용산구 새창로14길 49 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athletetraininglab</t>
+          <t>https://open.kakao.com/o/sgZjHSli</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1082,22 +1082,22 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q7" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1046370565</t>
+          <t>2036620060</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046370565</t>
+          <t>https://m.place.naver.com/place/2036620060</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 한남점</t>
+          <t>띵크아워핏PT 신용산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>think_ourdaily@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1477-2603</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
+          <t>서울특별시 용산구 한강대로 95 용산 래미안 더 센트럴 B2층 251호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://blog.naver.com/think_ourdaily</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2084933660</t>
+          <t>1991688832</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084933660</t>
+          <t>https://m.place.naver.com/place/1991688832</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이트레이너짐 PT 이태원점</t>
+          <t>릴리즈 운동센터 PT 공덕</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mytrainergym@naver.com</t>
+          <t>release1123@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1347-2166</t>
+          <t>0507-1319-1536</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
+          <t>서울특별시 용산구 새창로 70 상가동 408호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/mytrainergym105</t>
+          <t>https://blog.naver.com/release1123</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>185</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
-        <v>273</v>
+        <v>53</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1307063449</t>
+          <t>2006797617</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1307063449</t>
+          <t>https://m.place.naver.com/place/2006797617</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>민트니스</t>
+          <t>PT 필라테스 바디컨설팅 숙대점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mintness0218@naver.com</t>
+          <t>dailytk@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1367-5479</t>
+          <t>070-5066-6149</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+          <t>서울특별시 용산구 한강대로 304 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/xExbOq0i</t>
+          <t>http://pf.kakao.com/_FuhGG/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1364,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>77</v>
+        <v>2440</v>
       </c>
       <c r="Q10" t="n">
-        <v>1048</v>
+        <v>1263</v>
       </c>
       <c r="R10" t="n">
-        <v>1125</v>
+        <v>3703</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1620428153</t>
+          <t>35431442</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620428153</t>
+          <t>https://m.place.naver.com/place/35431442</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1406,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘피PT&amp;필라테스</t>
+          <t>망고짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leo920617@naver.com</t>
+          <t>mangogym2004@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1318-8437</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
+          <t>서울특별시 용산구 한강대로 282 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lp.pt_pilates</t>
+          <t>https://www.instagram.com/mangogym2004</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>197</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="R11" t="n">
-        <v>334</v>
+        <v>41</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1474,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1420244365</t>
+          <t>1820052873</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420244365</t>
+          <t>https://m.place.naver.com/place/1820052873</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1499,39 +1491,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>종합사회복지관</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에이펙스 이엠에스 스튜디오 용산점</t>
+          <t>효창종합사회복지관</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>apexems1@naver.com</t>
+          <t>funfun_hyochang@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1489-0892</t>
+          <t>02-716-0600</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>서울 용산구 한강대로 69 상가동 지하 1층 비 114-1호</t>
+          <t>서울특별시 용산구 효창원로 146-12 효창종합사회복지관</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://apexems.creatorlink.net/</t>
+          <t>http://www.hyochang.or.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1546,14 +1538,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w3t5</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1565,13 +1553,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>252</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>586</v>
+        <v>44</v>
       </c>
       <c r="R12" t="n">
-        <v>838</v>
+        <v>46</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,15 +1568,8529 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1672804681</t>
+          <t>12173893</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1672804681</t>
+          <t>https://m.place.naver.com/place/12173893</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>카디오팩토리</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cardiofactory@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1434-8978</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로81길 3 시온캐슬용산오피스텔 지하2층 1호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cardiofactory.official</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>20</v>
+      </c>
+      <c r="R13" t="n">
+        <v>51</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2060200393</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2060200393</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>핏클럽 서울</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ficlubseoul@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1388-5996</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 녹사평대로 240 204호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitclubseoul_official</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>120</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>35306784</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35306784</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LIM FIT 한남</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>czvx0317@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1309-9317</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로 76 403호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/czvx0317</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>132</v>
+      </c>
+      <c r="R15" t="n">
+        <v>167</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1798968279</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1798968279</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>후암PT</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>relaxpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1488-1022</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 후암로 41 201호</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/relaxpt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>13</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1366563601</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1366563601</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>권투,복싱</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>용산 탑복싱</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>akrsozhcl@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1374-1356</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 68 영천빌딩 2층 201호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ys_topboxing?igsh=OTFsa2x0djQ1MDQz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>55</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2024854978</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024854978</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-8046-4539</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 용문동</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1601891152</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1601891152</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>망고짐</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mangogym2004@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1445-1039</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 282 3층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mangogym2004</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>128</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20599215</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/20599215</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>마음다짐</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>maeumdagym@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>02-6368-7665</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로87길 54 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>21</v>
+      </c>
+      <c r="R20" t="n">
+        <v>31</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1637818623</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1637818623</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>인서울핏 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>qkrqh0728@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1337-4673</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 회나무로6길 5 혜광빌딩 지층</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/in_seoul_fit_01?igsh=MTM3dXNvdWMxMzYw</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>93</v>
+      </c>
+      <c r="R21" t="n">
+        <v>364</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2011418027</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2011418027</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>후핏</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>wjsrjs12@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1305-7665</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 274 우진상가 2층</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hoo_fit_official/</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>89</v>
+      </c>
+      <c r="R22" t="n">
+        <v>165</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1063476706</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1063476706</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>워너블짐 용산점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>swwnb@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1394-8593</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로43길 8 벽산메가트리움 상가동 104동 B1층</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/swwnb</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>1699</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>837</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2536</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1359393510</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1359393510</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>스튜디오에이 필라테스 용산점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>studio_a_blog@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1354-3027</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 리첸시아용산 A동 201호 스튜디오에이</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/studio_a_blog</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>136</v>
+      </c>
+      <c r="R24" t="n">
+        <v>290</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>897241223</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/897241223</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>070-8173-4014</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창동</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1057830175</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057830175</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>민트니스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mintness0218@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1367-5479</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로14길 43-2 4층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://naver.me/xExbOq0i</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1048</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1125</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1620428153</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1620428153</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>이스트핏</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>iforu2@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>02-792-7700</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로88길 16 미학빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>11</v>
+      </c>
+      <c r="R27" t="n">
+        <v>11</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>35221698</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35221698</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>드래곤짐</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hyeonseo2513@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1355-6163</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 29 지하1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>31</v>
+      </c>
+      <c r="R28" t="n">
+        <v>34</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1563064110</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1563064110</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F45 신용산</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>afterthis12@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 37 지하 1층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/f45_sinyongsan?igsh=MWg4ZWhxbDlkc2hpOQ%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>22</v>
+      </c>
+      <c r="R29" t="n">
+        <v>60</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1526678347</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526678347</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>이태원짐</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>itaewon_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1375-3752</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로 145 하나은행 건물6층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/itaewon_gym</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>720</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>329</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1049</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1379530021</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379530021</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>시각디자인</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>얼리디</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>jamesconsulting@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로41길 69 5층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>http://earlyd.co.kr</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1691373047</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691373047</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>뷰티플에볼루션</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bevolution@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1343-4362</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 장문로 74 3층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/beautiful_evolution</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>77</v>
+      </c>
+      <c r="R32" t="n">
+        <v>88</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>35228324</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35228324</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>DNA STUDIO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>dna_design@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1396-0816</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 소월로44길 9 2층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/dnastudio.seoul</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>9</v>
+      </c>
+      <c r="R33" t="n">
+        <v>10</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1758255780</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1758255780</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>레브 트레이닝 스튜디오</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>revpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1445-9602</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 유엔빌리지1길 18 . 101호</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/revpt</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>84</v>
+      </c>
+      <c r="R34" t="n">
+        <v>87</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>35407627</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35407627</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>만리체육관</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>knhpallc@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1370-8883</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창원로 270 만리체육관</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/knhpallc</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>330</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>303</v>
+      </c>
+      <c r="R35" t="n">
+        <v>633</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1676582421</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1676582421</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>바를정스튜디오필라테스&amp;자이로토닉</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>bareuljeong_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 210-13 4층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bareuljeong_studio</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>57</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1242618372</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1242618372</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MCTGYM용문</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mctfitness7@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1423-7537</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로41길 69 3층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://mctgym.com</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>71</v>
+      </c>
+      <c r="R37" t="n">
+        <v>157</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2031556968</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2031556968</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>살롱드핏</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jjeuneu@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>02-6951-0357</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로15길 21-1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>http://www.salondefit.co.kr/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>15</v>
+      </c>
+      <c r="R38" t="n">
+        <v>17</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1042050006</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1042050006</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>상떼PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bdkids90@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1392-1834</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로58길 3 지하1층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sante.pt</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>60</v>
+      </c>
+      <c r="R39" t="n">
+        <v>160</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1660572271</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1660572271</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>실내골프연습장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>내셔널짐 피티앤골프</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>national_gym_pt_golf@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 리첸시아상가 A동 B1F</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/national_gym_pt_golf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>212</v>
+      </c>
+      <c r="R40" t="n">
+        <v>539</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1312022957</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1312022957</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>칼라퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jadorer@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1312-4013</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 259-1 2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jadorer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>94</v>
+      </c>
+      <c r="R41" t="n">
+        <v>254</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>78644547</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/78644547</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>인터내셔널 필라테스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>internationalpilates@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1339-2733</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 78 고은빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/international.pilates</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>57</v>
+      </c>
+      <c r="R42" t="n">
+        <v>117</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1650827956</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650827956</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>지니핏바디스튜디오</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>miruda457@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1399-3667</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 210 대성빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness_jin</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>16</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1919612630</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1919612630</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>반트피티</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>vant-pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1325-9999</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로64길 26 4층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vantgym/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>6</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1427845417</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1427845417</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>VVIP P.T샵</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sukja7820@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1430-0868</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로75길 6 지층 11호</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>27</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1952684321</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1952684321</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GYM NOW 용산</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gymnowpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1354-8487</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 용산센트럴파크 Mall C동 2층 GYM NOW</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.gymnow.co.kr/</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>171</v>
+      </c>
+      <c r="R46" t="n">
+        <v>204</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1697851491</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1697851491</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>뉴런</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 69 지하102-2호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>37</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1446451207</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1446451207</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>텐세그리티 피트니스 클럽</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>tensegrity1103@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1368-3369</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 두텁바위로60길 49 대원정사 본관 2층 201호</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tensegrity_fit</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>130</v>
+      </c>
+      <c r="R48" t="n">
+        <v>174</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1139423406</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1139423406</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>070-8046-4459</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로1가</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1321677183</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1321677183</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>웰니스짐</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wlspt@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>02-795-9966</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 회나무로26길 12 지하1층 웰니스짐</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>19</v>
+      </c>
+      <c r="R50" t="n">
+        <v>33</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>11666525</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11666525</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>하프앤하프 필라테스피티</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>halfandhalf_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1446-8612</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 회나무로13길 34 2층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/halfandhalf_studio</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>29</v>
+      </c>
+      <c r="R51" t="n">
+        <v>43</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2037925715</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037925715</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>경영컨설팅</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GH 운동연구소</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>musclelab_9609@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크 타워동 8층 808호</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://goodhabitpt.com/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>11</v>
+      </c>
+      <c r="R52" t="n">
+        <v>15</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1126683355</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1126683355</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>센트럴짐</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>centralgym_0301@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1473-9317</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크타워 업무동 B1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/centralgym_0301/223941821798</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>1834</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1990</v>
+      </c>
+      <c r="R53" t="n">
+        <v>3824</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1063160702</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1063160702</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>에이블짐 이태원점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ablegym11@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1469-8181</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로27나길 40 준아트빌 지하 1층 에이블짐 휘트니스</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/13/bizes/364226?theme=place&amp;entry=pll&amp;lang=ko&amp;area=pll</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>757</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>656</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1413</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1674730307</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1674730307</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>모어피클 센트럴파크점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>haus5345pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 17 센트럴파크101동 Mall A 2층57~61호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/haus5345pt</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>375</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>336</v>
+      </c>
+      <c r="R55" t="n">
+        <v>711</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1176644355</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1176644355</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>웰페리온 SPA &amp; FITNESS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>wellperion@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1467-1339</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 413</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://litt.ly/wellperion</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>398</v>
+      </c>
+      <c r="R56" t="n">
+        <v>504</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1048457693</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1048457693</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>팀짐</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>osbum1478@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1407-4623</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로34길 22 6층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/timgymptstudio</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>12</v>
+      </c>
+      <c r="R57" t="n">
+        <v>14</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1208224902</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1208224902</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>인필라테스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>inpila51@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1387-1791</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 51 407호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/inpila51</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>425</v>
+      </c>
+      <c r="R58" t="n">
+        <v>510</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1384287931</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1384287931</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SYCAMORE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sycamoretree-@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1428-1710</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이태원로 217 306-3호 시크모어</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sycamoretree-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>31</v>
+      </c>
+      <c r="R59" t="n">
+        <v>38</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>36886876</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36886876</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>라온휘트니스&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>laonfittnes@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1322-4766</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창원로 132 B1 라온휘트니스</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/laonfittnes</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>484</v>
+      </c>
+      <c r="R60" t="n">
+        <v>643</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1025506921</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025506921</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>웅스핏</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>woongsfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0505-674-4935</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로34길 29 000</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://workofart.tistory.com/m/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>3</v>
+      </c>
+      <c r="R61" t="n">
+        <v>3</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1659324628</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1659324628</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LANCE&amp;J</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>boxofficenews@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>02-749-7498</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 유엔빌리지길 254 3층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://www.lanceandj.com/</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>9</v>
+      </c>
+      <c r="R62" t="n">
+        <v>12</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>21854010</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21854010</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>백투더바디</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>backtothebody@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>070-8648-1137</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 이촌로 248 한강맨션상가2층 11동205호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/backtothebody</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>22</v>
+      </c>
+      <c r="R63" t="n">
+        <v>26</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2015043750</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015043750</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>엘피PT&amp;필라테스</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>leo920617@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1318-8437</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 A동 2층 210호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lp.pt_pilates</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>137</v>
+      </c>
+      <c r="R64" t="n">
+        <v>334</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1420244365</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1420244365</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>동서 휘트니스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>dsfitness2011@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>02-714-2012</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 청파로 312</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dsfitness2011</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>17</v>
+      </c>
+      <c r="R65" t="n">
+        <v>68</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>37683773</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37683773</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>팀하드피트니스 한남점</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>teamhardfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1310-4252</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 67 402호</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/teamhardfitness</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>109</v>
+      </c>
+      <c r="R66" t="n">
+        <v>199</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1132822818</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132822818</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>에스웨이 피트니스 한남점</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>s_wayhn@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>02-795-0117</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 70 지하 1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/s_wayhn</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>228</v>
+      </c>
+      <c r="R67" t="n">
+        <v>398</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1787209299</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1787209299</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>트레이닝랩</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>traininglab@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1332-2285</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 회나무로39길 33</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/training_lab_kor/</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>111</v>
+      </c>
+      <c r="R68" t="n">
+        <v>142</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1331018379</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1331018379</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>스포벡휘트니스 숙대점</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>otamin@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1338-7207</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 296 참빛빌딩 지하1층</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/otamin</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>756</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>519</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1275</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1651442519</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1651442519</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>옥토버 필라테스</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ohsm3271@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1307-8309</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 새창로12길 3 2층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>12</v>
+      </c>
+      <c r="R70" t="n">
+        <v>52</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1299773934</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299773934</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>스포츠,레크레이션교육</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>짐구공 에듀 스페이스</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>gym90_gildong@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1475-2850</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 366 6층 605호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://gym90.creatorlink.net/</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>6</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1172794010</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1172794010</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MCTGYM 용산</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>mctfitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1375-7537</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 청파로 251 용산 다올 노블리움 지하1층</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@mct12</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1076</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1347</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1407110482</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1407110482</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>진핏메디컬PT운동센터</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>however79@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1336-4293</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로 76 한남프라자 4층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/however79</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>322</v>
+      </c>
+      <c r="R73" t="n">
+        <v>391</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>32625992</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32625992</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>라이닝 체형교정 운동센터</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>lining__hannam@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 89 4층</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lining__hannam/</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" t="n">
+        <v>20</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1722382488</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1722382488</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>재활공간 운동센터 신용산점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>rehabr@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1388-8381</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 95 비동 지하1층 162호, 166호</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rehabr</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1347</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1456</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1567327302</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1567327302</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>투비짐PT 신용산점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>tobegym2018@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1470-1432</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 69 용산 푸르지오 써밋 3층 To Be GYM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tobegym2018</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>277</v>
+      </c>
+      <c r="R76" t="n">
+        <v>318</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1493218485</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1493218485</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>가설자재,비티아시바피티아시바,난간대파이프판매,임대설치</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>070-8173-9725</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 용문동</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1409015966</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1409015966</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>버닝라이프</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>burnshadows@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1479-0011</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 70 3층 302호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>http://cafe.naver.com/burninglife</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>8</v>
+      </c>
+      <c r="R78" t="n">
+        <v>9</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1998396026</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998396026</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>가설자재비티아시바피티아시바발안전난간대판매임대설치</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>rodtmdu12@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>070-8083-9473</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창동</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1875168882</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1875168882</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>크로스핏 알앤엘 용산</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>crossfitrnl_su@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1386-8898</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 295 B1층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/crossfit_rnl_yongsan</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>62</v>
+      </c>
+      <c r="R80" t="n">
+        <v>189</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1771175314</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1771175314</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>070-8046-4366</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 후암동</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1150696241</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1150696241</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>H 퍼스널트레이닝 한남</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>hp4566@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1419-4566</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로 76 403호</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hp4566</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>162</v>
+      </c>
+      <c r="R82" t="n">
+        <v>175</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>35058160</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35058160</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>파프짐 한남PT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>finest2010@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1343-7012</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 97 B2 PAFGYM</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://www.pafgym.com/</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>175</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>290</v>
+      </c>
+      <c r="R83" t="n">
+        <v>465</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1935905709</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1935905709</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>대림아시바BT비티피티아시바비계설치발판유로폼난간대대림가설</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>070-8046-4552</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서계동</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1409440582</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1409440582</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>비케이핏</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>fiftyfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>info@bkfitseoul.com</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1369-6898</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 보광로 109 2층</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.bkfitseoul.com</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>6</v>
+      </c>
+      <c r="R85" t="n">
+        <v>15</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1587565217</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587565217</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>마이트레이너짐 PT 이태원점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mytrainergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1347-2166</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 보광로59길 40 202호 마이트레이너짐</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/mytrainergym105</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>185</v>
+      </c>
+      <c r="R86" t="n">
+        <v>273</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1307063449</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1307063449</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>마이트레이너짐 PT 한남점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>mytrainergym@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1477-2603</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 71 지1층 2호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/mytrainergym105</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2084933660</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084933660</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>번역,통역서비스</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>오라티오</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>red4575@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>02-798-3917</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로 60</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>http://oratio.co.kr/</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>18184001</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/18184001</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>소수짐 한남</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sosoogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1393-1151</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 대사관로 56 3층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sosoogym</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>93</v>
+      </c>
+      <c r="R89" t="n">
+        <v>110</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1713445680</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1713445680</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>더템플짐 그룹 트레이닝 &amp; PT</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>doing991210@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1338-7118</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 신흥로 13-1 지하1층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_temple_hbc</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>10</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2053773685</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053773685</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>맹그로브 짐</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>mangrovegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>070-4212-4882</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한남대로20길 47-9 지하1층</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mangrovegym</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>33</v>
+      </c>
+      <c r="R91" t="n">
+        <v>57</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1337443580</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337443580</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>훈짐</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>hoongym@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>02-6953-6273</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 효창원로48길 6 B1층(용문동)</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>15</v>
+      </c>
+      <c r="R92" t="n">
+        <v>31</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1874669992</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1874669992</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>밸런스 핏</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>alsrn8046@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1397-6377</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 청파로47길 49 캠퍼스프라자 4층</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/alsrn8046</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>187</v>
+      </c>
+      <c r="R93" t="n">
+        <v>629</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>10976486</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/10976486</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>위워크아웃PT</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>weworkout@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1390-6895</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 후암로 41 2층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/weworkout</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>12</v>
+      </c>
+      <c r="R94" t="n">
+        <v>51</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1025030146</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1025030146</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>에스퍼스널트레이닝</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>spt2014@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 서빙고로 67 파크타워 1층 상가27호</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spt2014</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>3</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>35287673</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35287673</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>내셔널짐 PT 용산점</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>national_gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 리첸시아상가 A동 3층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/national_gym</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>236</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>100</v>
+      </c>
+      <c r="R96" t="n">
+        <v>336</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1006850843</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006850843</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>와이짐</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>gym-y@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1437-7441</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 장문로19길 4 3층(보광동, (주)동양과학)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>2069637704</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2069637704</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>F45 한남</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>thesweeeet@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>hannam@f45training.kr</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 독서당로 70 현대리버티하우스 404호</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>http://f45training.kr/hannam/</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>117</v>
+      </c>
+      <c r="R98" t="n">
+        <v>247</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>1976880734</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1976880734</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>이루어GYM</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>be_achieved@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1345-6312</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 원효로 255 2층</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>26</v>
+      </c>
+      <c r="R99" t="n">
+        <v>113</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1050482926</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050482926</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>스카이짐 헬스 24시</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>pilatessky@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1433-3993</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 273 용산빌딩 B1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skygym__</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>739</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>101</v>
+      </c>
+      <c r="R100" t="n">
+        <v>840</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1175973317</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1175973317</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>스포짐 용산점</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>spogym1577@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>02-701-0011</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 백범로 341 리첸시아 용산B</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/spogym1577</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>1802</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>2078</v>
+      </c>
+      <c r="R101" t="n">
+        <v>3880</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>31155915</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31155915</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>제이핏</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jayfit_yongsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1437-0878</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 한강대로 56-1 4층 제이핏</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jayfit_yongsan/223747712852</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>7</v>
+      </c>
+      <c r="R102" t="n">
+        <v>24</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1545094395</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1545094395</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>마이 페이보릿 리커버리</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>athletetraininglab@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1356-4024</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>서울특별시 용산구 만리재로 178 4층 마이페이보릿 리커버리</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/athletetraininglab</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>34</v>
+      </c>
+      <c r="R103" t="n">
+        <v>75</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1046370565</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1046370565</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
